--- a/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>ANTE</t>
   </si>
@@ -656,241 +656,254 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43281</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43100</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>42916</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42735</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42551</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-8500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-4300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-3800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-14700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>-20500</v>
       </c>
       <c r="P10" s="3">
         <v>-20500</v>
       </c>
       <c r="Q10" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="R10" s="3">
         <v>-12100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +922,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,22 +935,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
       </c>
       <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -959,8 +973,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1009,16 +1026,19 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>4500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1026,29 +1046,29 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>67300</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1059,8 +1079,11 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1109,8 +1132,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1126,108 +1152,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>10400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>78200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>60500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>45900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-4600</v>
       </c>
       <c r="I18" s="3">
         <v>-4600</v>
       </c>
       <c r="J18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-23700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-111300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-67500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-38400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1246,58 +1279,62 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1346,8 +1383,11 @@
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1396,58 +1436,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-109400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-35500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1458,46 +1504,49 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1546,108 +1595,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-109600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-67000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-54700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-71600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-104100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-52400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1696,8 +1754,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1725,8 +1786,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1743,11 +1804,14 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1796,8 +1860,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1846,108 +1913,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-71600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-104100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-52400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1996,113 +2072,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-71600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-104100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-52400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43281</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43100</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>42916</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42735</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42551</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2121,8 +2206,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2141,75 +2227,79 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>117500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>218600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>123900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2100</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -2226,8 +2316,8 @@
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2236,63 +2326,69 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>3600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>13200</v>
       </c>
       <c r="N43" s="3">
         <v>13200</v>
       </c>
       <c r="O43" s="3">
+        <v>13200</v>
+      </c>
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2341,208 +2437,223 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E45" s="3">
         <v>65100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>64200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>47900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>70000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>95400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>77100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>188800</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E46" s="3">
         <v>69800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>66400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>79900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>160400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>205200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>272700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E47" s="3">
         <v>34100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>36400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>100300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>102400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>83900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>90200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E48" s="3">
         <v>10900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>61000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2580,19 +2691,22 @@
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>1500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2641,8 +2755,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2691,58 +2808,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>400</v>
       </c>
       <c r="F52" s="3">
+        <v>400</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>900</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
       </c>
       <c r="K52" s="3">
+        <v>900</v>
+      </c>
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>49300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2791,58 +2914,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E54" s="3">
         <v>115100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>125600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>98900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>128800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>203200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>225000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>334200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>381200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>457900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2861,8 +2990,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2881,93 +3011,97 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E57" s="3">
         <v>15800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>46200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>48500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E58" s="3">
         <v>12800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>6100</v>
       </c>
       <c r="L58" s="3">
         <v>6100</v>
       </c>
       <c r="M58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="N58" s="3">
         <v>6200</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -2978,111 +3112,120 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E59" s="3">
         <v>73200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>67300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>71400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>85900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>50700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>204900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E60" s="3">
         <v>101800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>105000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>113800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>117800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>113500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>116000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>112700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>102400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>67300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>238800</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3096,26 +3239,26 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>2600</v>
       </c>
       <c r="I61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J61" s="3">
         <v>2500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3131,8 +3274,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3152,37 +3298,40 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>24700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3231,8 +3380,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3281,8 +3433,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3331,58 +3486,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E66" s="3">
         <v>69400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>65800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>111100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>112500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>254300</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3401,8 +3562,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3451,8 +3613,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3501,8 +3666,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3551,8 +3719,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3601,58 +3772,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-322200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-318200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-306700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-304900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-292800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-299100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-293900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-267200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-262400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-190900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-172300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-68300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3701,8 +3878,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3751,8 +3931,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3801,58 +3984,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E76" s="3">
         <v>45800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>51400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>147600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>223100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>355200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>211900</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3901,113 +4090,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43281</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43100</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>42916</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42735</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42551</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-71600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-104100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-52400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4026,8 +4224,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4076,8 +4275,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4126,8 +4328,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4176,8 +4381,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4226,8 +4434,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4276,8 +4487,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4326,8 +4540,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4376,8 +4593,11 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4396,8 +4616,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4446,8 +4667,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4496,8 +4720,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4546,8 +4773,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4596,8 +4826,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4616,8 +4849,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4666,8 +4900,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4716,8 +4953,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4766,8 +5006,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4816,8 +5059,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4866,8 +5112,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4916,8 +5165,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4964,6 +5216,9 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>ANTE</t>
   </si>
@@ -656,148 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
-        <v>400</v>
-      </c>
       <c r="F8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,105 +812,111 @@
         <v>1400</v>
       </c>
       <c r="E9" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="F9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G9" s="3">
         <v>2400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-900</v>
       </c>
-      <c r="E10" s="3">
-        <v>-2500</v>
-      </c>
       <c r="F10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-5000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-8500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-14700</v>
-      </c>
-      <c r="P10" s="3">
-        <v>-20500</v>
       </c>
       <c r="Q10" s="3">
         <v>-20500</v>
       </c>
       <c r="R10" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="S10" s="3">
         <v>-12100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -923,8 +936,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -938,23 +952,23 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
@@ -976,8 +990,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1029,50 +1046,53 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>4500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>67300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1082,8 +1102,11 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1135,8 +1158,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1153,114 +1179,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
-        <v>10400</v>
-      </c>
       <c r="F17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G17" s="3">
         <v>6600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>124400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>78200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>60500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>45900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000</v>
       </c>
-      <c r="E18" s="3">
-        <v>-10000</v>
-      </c>
       <c r="F18" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-4600</v>
       </c>
       <c r="J18" s="3">
         <v>-4600</v>
       </c>
       <c r="K18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L18" s="3">
         <v>-23700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-111300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-67500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-51500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-38400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1280,61 +1313,65 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1300</v>
-      </c>
       <c r="F20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1386,8 +1423,11 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1439,61 +1479,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3700</v>
       </c>
-      <c r="E23" s="3">
-        <v>-11300</v>
-      </c>
       <c r="F23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-109400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-66600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-49300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-35500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1507,46 +1553,49 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1598,114 +1647,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3700</v>
       </c>
-      <c r="E26" s="3">
-        <v>-11300</v>
-      </c>
       <c r="F26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-109600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
-        <v>-11600</v>
-      </c>
       <c r="F27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-71600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-104100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-37000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1757,31 +1815,34 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-6300</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1789,8 +1850,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -1807,11 +1868,14 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1863,8 +1927,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1916,114 +1983,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
-        <v>1300</v>
-      </c>
       <c r="F32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
-        <v>-11600</v>
-      </c>
       <c r="F33" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-71600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-104100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-37000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2075,119 +2151,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
-        <v>-11600</v>
-      </c>
       <c r="F35" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-71600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-104100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-37000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2207,8 +2292,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2228,82 +2314,86 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>117500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>218600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>123900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
       </c>
@@ -2319,8 +2409,8 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2329,66 +2419,72 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>3600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>13200</v>
       </c>
       <c r="O43" s="3">
         <v>13200</v>
       </c>
       <c r="P43" s="3">
+        <v>13200</v>
+      </c>
+      <c r="Q43" s="3">
         <v>10900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2440,220 +2536,235 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E45" s="3">
         <v>28500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>65100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>64200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>47900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>70000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>95400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>77100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>188800</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E46" s="3">
         <v>29400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>63600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>66400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>79900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>98600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>160400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>205200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>272700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E47" s="3">
         <v>30700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>36400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>42500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>45500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>46300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>102000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>83900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>90200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E48" s="3">
         <v>10500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2694,19 +2805,22 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2758,8 +2872,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2811,61 +2928,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>400</v>
       </c>
       <c r="F52" s="3">
         <v>400</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>49300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2917,61 +3040,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E54" s="3">
         <v>70600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>115100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>98900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>95800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>128800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>129800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>203200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>225000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>334200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>381200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>457900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2991,8 +3120,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3012,100 +3142,104 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E57" s="3">
         <v>16500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>46200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>48500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>40400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>9900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>6100</v>
       </c>
       <c r="M58" s="3">
         <v>6100</v>
       </c>
       <c r="N58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="O58" s="3">
         <v>6200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3115,117 +3249,126 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E59" s="3">
         <v>69500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>67300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>71400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>85900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>76400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>204900</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E60" s="3">
         <v>95800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>101800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>105000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>98000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>113800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>113500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>116000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>112700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>102400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>90200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>67300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>238800</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3242,26 +3385,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>2600</v>
       </c>
       <c r="J61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3277,13 +3420,16 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -3301,37 +3447,40 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>24700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3383,8 +3532,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3436,8 +3588,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3489,61 +3644,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E66" s="3">
         <v>63700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>65800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>83500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>79900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>77200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>111100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>254300</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3563,8 +3724,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3616,8 +3778,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3669,8 +3834,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3722,8 +3890,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3775,61 +3946,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-318800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-322200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-318200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-306700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-304900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-292800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-286400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-299100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-293900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-267200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-262400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-190900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-172300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-68300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-15800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3881,8 +4058,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3934,8 +4114,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3987,61 +4170,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>51400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>126600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>147600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>223100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>268700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>355200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>211900</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4093,119 +4282,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
-        <v>-11600</v>
-      </c>
       <c r="F81" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-71600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-104100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-37000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4225,8 +4423,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4278,8 +4477,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4331,8 +4533,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4384,8 +4589,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4437,8 +4645,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4490,8 +4701,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4543,8 +4757,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4596,8 +4813,11 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4617,8 +4837,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4670,8 +4891,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4723,8 +4947,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4776,8 +5003,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4829,8 +5059,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4850,8 +5083,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4903,8 +5137,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4956,8 +5193,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5009,8 +5249,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5062,8 +5305,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5115,8 +5361,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5168,8 +5417,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5219,6 +5471,9 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>ANTE</t>
   </si>
@@ -656,18 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -679,244 +678,270 @@
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>800</v>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E8" s="3">
-        <v>500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2500</v>
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
-        <v>2900</v>
+        <v>300</v>
       </c>
       <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>8800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>11300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>13200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>14700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>13100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2400</v>
+        <v>100</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H9" s="3">
-        <v>7900</v>
+        <v>400</v>
       </c>
       <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>6800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>11100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>21700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>11900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>18500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>27800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>31200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>29500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>19600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H10" s="3">
-        <v>-5000</v>
+        <v>-100</v>
       </c>
       <c r="I10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-8500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-3800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-20500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-20500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-12100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,44 +962,46 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
-        <v>200</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
@@ -993,8 +1020,14 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1049,31 +1082,37 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4500</v>
+      <c r="D14" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>300</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1085,51 +1124,57 @@
         <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>67300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1161,8 +1206,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1180,120 +1231,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4700</v>
+        <v>1300</v>
       </c>
       <c r="E17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6600</v>
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="3">
-        <v>12400</v>
+        <v>1400</v>
       </c>
       <c r="I17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>13300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>15900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>36900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>22500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>37300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>36000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>124400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>78200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>60500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>45900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3900</v>
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-4100</v>
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H18" s="3">
-        <v>-9500</v>
+        <v>-1100</v>
       </c>
       <c r="I18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-9700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-27400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-21300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-111300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-67500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-51500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-38400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1314,87 +1379,95 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3100</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H20" s="3">
-        <v>-1400</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>6400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>6800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1426,8 +1499,14 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1437,20 +1516,20 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1482,120 +1561,138 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>100</v>
+        <v>10700</v>
       </c>
       <c r="E23" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1000</v>
+        <v>10700</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H23" s="3">
-        <v>-10900</v>
+        <v>-1500</v>
       </c>
       <c r="I23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>-6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-27800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-20400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-109400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-66600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-49300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-35500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
+        <v>5400</v>
+      </c>
+      <c r="U24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>700</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
-      </c>
-      <c r="R24" s="3">
-        <v>5400</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1650,120 +1747,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>10700</v>
       </c>
       <c r="E26" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1000</v>
+        <v>10700</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H26" s="3">
-        <v>-11100</v>
+        <v>-1500</v>
       </c>
       <c r="I26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>-6700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>12000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-28400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-20700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-20400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-67000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-54700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-34500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-300</v>
+        <v>9900</v>
       </c>
       <c r="E27" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1800</v>
+        <v>9900</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H27" s="3">
-        <v>-10900</v>
+        <v>-2000</v>
       </c>
       <c r="I27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>-6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>12700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-26700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-71600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-104100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-52400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-37000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-28600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1818,46 +1933,52 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-300</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="I29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -1871,11 +1992,17 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1930,8 +2057,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1986,120 +2119,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3100</v>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-6400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-6800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-600</v>
+        <v>9900</v>
       </c>
       <c r="E33" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1800</v>
+        <v>9900</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H33" s="3">
-        <v>-10900</v>
+        <v>-2000</v>
       </c>
       <c r="I33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>-6500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-26700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-71600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-104100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-52400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-37000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-28600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2154,125 +2305,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-600</v>
+        <v>9900</v>
       </c>
       <c r="E35" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1800</v>
+        <v>9900</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H35" s="3">
-        <v>-10900</v>
+        <v>-2000</v>
       </c>
       <c r="I35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>-6500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-26700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-71600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-104100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-52400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-37000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-28600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2293,8 +2462,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2315,91 +2486,99 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K41" s="3">
+        <v>900</v>
+      </c>
+      <c r="L41" s="3">
+        <v>300</v>
+      </c>
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
-        <v>900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>54100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>117500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>218600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>123900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H42" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
@@ -2412,102 +2591,114 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>3600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>21500</v>
       </c>
       <c r="E43" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>22100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>22100</v>
+      </c>
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>2300</v>
-      </c>
       <c r="I43" s="3">
+        <v>800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>25300</v>
+      </c>
+      <c r="K43" s="3">
         <v>7100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>11800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>11100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>13200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>13200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>10900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>10600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>12000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2539,240 +2730,270 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29600</v>
+        <v>23500</v>
       </c>
       <c r="E45" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H45" s="3">
         <v>28500</v>
       </c>
-      <c r="F45" s="3">
-        <v>65100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>64200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>32200</v>
-      </c>
       <c r="I45" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K45" s="3">
         <v>27500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>47900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>26900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>29500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>44500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>42900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>62400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>70000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>95400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>77100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>38500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>188800</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="F46" s="3">
         <v>29900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>29900</v>
+      </c>
+      <c r="H46" s="3">
         <v>29400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>29400</v>
+      </c>
+      <c r="J46" s="3">
         <v>69800</v>
       </c>
-      <c r="G46" s="3">
-        <v>71300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>36600</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>37600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>58600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>40200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>38900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>63600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>66400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>79900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>98600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>160400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>205200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>272700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F47" s="3">
         <v>32000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
+        <v>32000</v>
+      </c>
+      <c r="H47" s="3">
         <v>30700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J47" s="3">
         <v>34100</v>
       </c>
-      <c r="G47" s="3">
-        <v>36400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>39600</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>41200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>42500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>41000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>43000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>45500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>46300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>100300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>102400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>102000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>83900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>90200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F48" s="3">
         <v>10200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H48" s="3">
         <v>10500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J48" s="3">
         <v>10900</v>
       </c>
-      <c r="G48" s="3">
-        <v>17500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>19300</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>19400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>14900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>16100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>13500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>39900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>61000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>43700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2808,19 +3029,25 @@
         <v>0</v>
       </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
         <v>1500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2875,8 +3102,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2931,64 +3164,76 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>500</v>
-      </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
       </c>
       <c r="K52" s="3">
+        <v>800</v>
+      </c>
+      <c r="L52" s="3">
+        <v>400</v>
+      </c>
+      <c r="M52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>8100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>8500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>30400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>29400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>49300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3043,64 +3288,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>96400</v>
+      </c>
+      <c r="F54" s="3">
         <v>72200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>72200</v>
+      </c>
+      <c r="H54" s="3">
         <v>70600</v>
       </c>
-      <c r="F54" s="3">
-        <v>115100</v>
-      </c>
-      <c r="G54" s="3">
-        <v>125600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>96000</v>
-      </c>
       <c r="I54" s="3">
-        <v>98900</v>
+        <v>70600</v>
       </c>
       <c r="J54" s="3">
         <v>115100</v>
       </c>
       <c r="K54" s="3">
+        <v>98900</v>
+      </c>
+      <c r="L54" s="3">
+        <v>115100</v>
+      </c>
+      <c r="M54" s="3">
         <v>95800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>97700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>128800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>129800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>203200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>225000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>334200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>381200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>457900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3121,8 +3378,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3143,64 +3402,72 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="H57" s="3">
         <v>16500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>16500</v>
+      </c>
+      <c r="J57" s="3">
         <v>15800</v>
       </c>
-      <c r="G57" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>18400</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>23200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>37400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>35500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>33400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>39300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>46200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>48500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>51700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>40400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>27200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3208,167 +3475,185 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>11100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>11100</v>
+      </c>
+      <c r="J58" s="3">
         <v>12800</v>
       </c>
-      <c r="G58" s="3">
-        <v>14400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>72800</v>
+        <v>66800</v>
       </c>
       <c r="E59" s="3">
-        <v>69500</v>
+        <v>66800</v>
       </c>
       <c r="F59" s="3">
-        <v>73200</v>
+        <v>69900</v>
       </c>
       <c r="G59" s="3">
-        <v>67300</v>
+        <v>69900</v>
       </c>
       <c r="H59" s="3">
-        <v>71400</v>
+        <v>57200</v>
       </c>
       <c r="I59" s="3">
+        <v>57200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>70100</v>
+      </c>
+      <c r="K59" s="3">
         <v>68800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>85900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>77100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>77900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>76400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>67200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>25800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>27300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>50700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>49800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>40100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>204900</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>81500</v>
+      </c>
+      <c r="F60" s="3">
         <v>84400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>84400</v>
+      </c>
+      <c r="H60" s="3">
         <v>95800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>95800</v>
+      </c>
+      <c r="J60" s="3">
         <v>101800</v>
       </c>
-      <c r="G60" s="3">
-        <v>98500</v>
-      </c>
-      <c r="H60" s="3">
-        <v>105000</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>98000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>113800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>117800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>113500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>116000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>112700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>78200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>75800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>102400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>90200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>67300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>238800</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3388,29 +3673,29 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>2600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2500</v>
       </c>
       <c r="L61" s="3">
         <v>2600</v>
       </c>
       <c r="M61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O61" s="3">
         <v>2700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3423,64 +3708,76 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F62" s="3">
         <v>8800</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>8800</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1100</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>24700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>25500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>24500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>24400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>25500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3535,8 +3832,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3591,8 +3894,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3647,64 +3956,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>60300</v>
+        <v>85100</v>
       </c>
       <c r="E66" s="3">
-        <v>63700</v>
+        <v>85100</v>
       </c>
       <c r="F66" s="3">
-        <v>69400</v>
+        <v>93300</v>
       </c>
       <c r="G66" s="3">
-        <v>65800</v>
+        <v>93300</v>
       </c>
       <c r="H66" s="3">
-        <v>71500</v>
+        <v>95800</v>
       </c>
       <c r="I66" s="3">
+        <v>95800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>101800</v>
+      </c>
+      <c r="K66" s="3">
         <v>67400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>83500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>79900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>77200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>82100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>78400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>76600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>77400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>111100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>112500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>102700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>254300</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3725,8 +4046,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3781,8 +4104,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3837,8 +4166,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3893,8 +4228,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3949,64 +4290,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-298900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-298900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-318800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>-318800</v>
+      </c>
+      <c r="H72" s="3">
         <v>-322200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
+        <v>-322200</v>
+      </c>
+      <c r="J72" s="3">
         <v>-318200</v>
       </c>
-      <c r="G72" s="3">
-        <v>-306700</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-304900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-292800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-286400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-299100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-293900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-267200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-262400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-190900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-172300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-68300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-15800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>21200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4061,8 +4414,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4117,8 +4476,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4173,64 +4538,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44200</v>
+      </c>
+      <c r="F76" s="3">
         <v>11800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>11800</v>
+      </c>
+      <c r="H76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J76" s="3">
         <v>45800</v>
       </c>
-      <c r="G76" s="3">
-        <v>59800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>24500</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>31500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>16000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>46700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>51400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>126600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>147600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>223100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>268700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>355200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>211900</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4285,125 +4662,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-600</v>
+        <v>9900</v>
       </c>
       <c r="E81" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-13300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1800</v>
+        <v>9900</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H81" s="3">
-        <v>-10900</v>
+        <v>-2000</v>
       </c>
       <c r="I81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>-6500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-26700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-71600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-104100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-52400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-37000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-28600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4424,31 +4819,33 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4480,8 +4877,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4536,8 +4939,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4592,8 +5001,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4648,8 +5063,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4704,8 +5125,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4760,31 +5187,37 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -4816,8 +5249,14 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4838,31 +5277,33 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-13600</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-13600</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4894,8 +5335,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4950,8 +5397,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5006,31 +5459,37 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5062,8 +5521,14 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5084,31 +5549,33 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5140,8 +5607,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5196,8 +5669,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5252,8 +5731,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5308,31 +5793,37 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+        <v>3000</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>-1200</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -5364,31 +5855,37 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5420,16 +5917,22 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -5438,10 +5941,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
@@ -5474,6 +5977,12 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANTE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>ANTE</t>
   </si>
@@ -656,19 +656,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -680,220 +679,240 @@
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42551</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
+      <c r="G8" s="3">
+        <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>8800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>12800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>14700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>13100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>6800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>11100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>21700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>11900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>14200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>18500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>27800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>31200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>29500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>19600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>22900</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
       </c>
       <c r="H10" s="3">
         <v>-100</v>
@@ -901,47 +920,53 @@
       <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
+      <c r="J10" s="3">
+        <v>-100</v>
       </c>
       <c r="K10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-8500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-3800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-14700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-20500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-20500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>-12100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -964,8 +989,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,27 +1014,27 @@
       <c r="I12" s="3">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>0</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1026,8 +1053,14 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1088,37 +1121,43 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-11800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-11800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1130,57 +1169,63 @@
         <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>67300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
-      </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1212,8 +1257,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1233,132 +1284,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>13300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>15900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>16800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>36900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>22500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>37300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>36000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>124400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>78200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>60500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>45900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>32600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>-4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-23700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-9700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-21300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-111300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-67500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-51500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-38400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1381,100 +1446,108 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>6400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>6800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
-        <v>200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J21" s="3">
-        <v>200</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1505,37 +1578,43 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1567,70 +1646,82 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3">
         <v>10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>10700</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-20400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-109400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-66600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-49300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-35500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1652,47 +1743,53 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-10200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1753,132 +1850,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3">
         <v>10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>10700</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>-6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>12000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-28400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-20400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-109600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-67000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-54700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-34500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-21700</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3">
         <v>9900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>9900</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>-6500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>12700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-18500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-104100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-52400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-37000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-28600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-19700</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1939,52 +2054,58 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-700</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>200</v>
+      </c>
+      <c r="I29" s="3">
+        <v>200</v>
+      </c>
+      <c r="J29" s="3">
         <v>-300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-300</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -1998,11 +2119,17 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2063,8 +2190,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2125,132 +2258,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-6400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-4200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3">
         <v>9900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>9900</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>-6500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-26700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-18500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-104100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-52400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-37000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-28600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2311,137 +2462,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3">
         <v>9900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>9900</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>-6500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-26700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-18500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-104100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-52400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-37000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-28600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42551</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2464,8 +2633,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2488,70 +2659,78 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>100</v>
+      </c>
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>54100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>117500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>218600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>123900</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2562,29 +2741,29 @@
         <v>200</v>
       </c>
       <c r="F42" s="3">
+        <v>200</v>
+      </c>
+      <c r="G42" s="3">
+        <v>200</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
@@ -2597,85 +2776,97 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>3600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F43" s="3">
         <v>21500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>21500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>22100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>22100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>25300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>7100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>10400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>11800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>11100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>8000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>13200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>13200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>10900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>10600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>12000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2700,11 +2891,11 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2736,271 +2927,301 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>23500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>23500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>28500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>28500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>47900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>26900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>29500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>44500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>42900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>62400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>70000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>95400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>77100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>38500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>188800</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F46" s="3">
         <v>54600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>54600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>29900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>29900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>29400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>29400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>69800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>37600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>58600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>40200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>38900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>63600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>66400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>79900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>98600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>160400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>205200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>272700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>27700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>27700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>32000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>32000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>30700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>30700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>34100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>41200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>42500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>41000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>43000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>45500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>46300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>100300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>102400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>102000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>83900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>90200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>17800</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>34300</v>
+      </c>
+      <c r="F48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>10200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>10200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>10500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>10500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>10900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>19400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>13700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>14900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>16100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>13500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>15400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>39900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>61000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>43700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -3035,19 +3256,25 @@
         <v>0</v>
       </c>
       <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
         <v>1500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3108,8 +3335,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3170,8 +3403,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3187,53 +3426,59 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>800</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>800</v>
+      </c>
+      <c r="N52" s="3">
+        <v>400</v>
+      </c>
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>8100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>8500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>30400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>29400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>49300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3294,70 +3539,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>60200</v>
+      </c>
+      <c r="F54" s="3">
         <v>96400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>96400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>72200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>72200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>70600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>70600</v>
-      </c>
-      <c r="J54" s="3">
-        <v>115100</v>
-      </c>
-      <c r="K54" s="3">
-        <v>98900</v>
       </c>
       <c r="L54" s="3">
         <v>115100</v>
       </c>
       <c r="M54" s="3">
+        <v>98900</v>
+      </c>
+      <c r="N54" s="3">
+        <v>115100</v>
+      </c>
+      <c r="O54" s="3">
         <v>95800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>97700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>128800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>129800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>203200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>225000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>334200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>381200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>457900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>466200</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3380,8 +3637,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3404,8 +3663,10 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3416,58 +3677,64 @@
         <v>11400</v>
       </c>
       <c r="F57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="H57" s="3">
         <v>11600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>16500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>16500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>23200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>22200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>37400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>35500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>33400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>39300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>46200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>48500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>51700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>40400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>27200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>33900</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3484,176 +3751,194 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>11100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>11100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>12800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>6200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>65400</v>
+      </c>
+      <c r="F59" s="3">
         <v>66800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>66800</v>
       </c>
-      <c r="F59" s="3">
-        <v>69900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>69900</v>
-      </c>
       <c r="H59" s="3">
+        <v>70900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>70900</v>
+      </c>
+      <c r="J59" s="3">
         <v>57200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>57200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>70100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>68800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>85900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>77100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>77900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>76400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>67200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>25800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>27300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>50700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>49800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>40100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>204900</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>78600</v>
+      </c>
+      <c r="F60" s="3">
         <v>81500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>81500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>84400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>84400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>95800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>95800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>101800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>98000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>113800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>117800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>113500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>116000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>112700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>78200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>75800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>102400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>90200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>67300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>238800</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3679,29 +3964,29 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>2600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2500</v>
       </c>
       <c r="N61" s="3">
         <v>2600</v>
       </c>
       <c r="O61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P61" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3714,8 +3999,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3726,58 +4017,64 @@
         <v>3600</v>
       </c>
       <c r="F62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H62" s="3">
         <v>8800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>8800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>24700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>25500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>24500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>24400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>25500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3838,8 +4135,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3900,8 +4203,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3962,70 +4271,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>82200</v>
+      </c>
+      <c r="F66" s="3">
         <v>85100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>85100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>93300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>93300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>95800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>95800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>101800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>67400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>83500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>79900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>77200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>82100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>78400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>76600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>77400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>111100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>112500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>102700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>254300</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4048,8 +4369,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4110,8 +4433,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4172,8 +4501,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4234,8 +4569,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4296,70 +4637,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-332500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-332500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-298900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-298900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-318800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-318800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-322200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-322200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-318200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-292800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-286400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-299100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-293900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-267200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-262400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-190900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-172300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-68300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-15800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>21200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-134000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4420,8 +4773,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4482,8 +4841,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4544,70 +4909,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F76" s="3">
         <v>44200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>44200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>45800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>31500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>31600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>46700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>51400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>126600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>147600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>223100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>268700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>355200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>211900</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4668,137 +5045,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42551</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42277</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3">
         <v>9900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>9900</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>-6500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-26700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-18500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-104100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-52400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-37000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-28600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4821,23 +5216,25 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4847,11 +5244,11 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4883,8 +5280,14 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4945,8 +5348,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5007,8 +5416,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5069,8 +5484,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5131,8 +5552,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5193,37 +5620,43 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -5255,8 +5688,14 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5279,23 +5718,25 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-13600</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5305,11 +5746,11 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5341,8 +5782,14 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5403,8 +5850,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5465,23 +5918,29 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5491,11 +5950,11 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -5527,8 +5986,14 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5551,8 +6016,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5577,11 +6044,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5613,8 +6080,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5675,8 +6148,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5737,8 +6216,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5799,37 +6284,43 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3000</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H100" s="3">
+        <v>600</v>
+      </c>
+      <c r="I100" s="3">
+        <v>600</v>
+      </c>
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -5861,23 +6352,29 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
@@ -5887,11 +6384,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5923,35 +6420,41 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3500</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1300</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -5983,6 +6486,12 @@
         <v>0</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>
